--- a/RaidenDemo/文档/配置表/EffectResource.xlsx
+++ b/RaidenDemo/文档/配置表/EffectResource.xlsx
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="236">
   <si>
     <t>##var</t>
   </si>
@@ -648,7 +648,145 @@
     <t>smoke_01</t>
   </si>
   <si>
-    <t>烟雾_小</t>
+    <t>爆炸烟雾_小</t>
+  </si>
+  <si>
+    <t>fire_small_1</t>
+  </si>
+  <si>
+    <t>火焰_小_1</t>
+  </si>
+  <si>
+    <t>fire_small_2</t>
+  </si>
+  <si>
+    <t>火焰_小_2</t>
+  </si>
+  <si>
+    <t>fire_small_3</t>
+  </si>
+  <si>
+    <t>火焰_小_3</t>
+  </si>
+  <si>
+    <t>fire_middle_1</t>
+  </si>
+  <si>
+    <t>火焰_中_1</t>
+  </si>
+  <si>
+    <t>fire_middle_2</t>
+  </si>
+  <si>
+    <t>火焰_中_2</t>
+  </si>
+  <si>
+    <t>fire_middle_3</t>
+  </si>
+  <si>
+    <t>火焰_中_3</t>
+  </si>
+  <si>
+    <t>fire_middle_4</t>
+  </si>
+  <si>
+    <t>火焰_中_4</t>
+  </si>
+  <si>
+    <t>fire_big_1</t>
+  </si>
+  <si>
+    <t>火焰_大_1</t>
+  </si>
+  <si>
+    <t>fire_big_2</t>
+  </si>
+  <si>
+    <t>火焰_大_2</t>
+  </si>
+  <si>
+    <t>fire_big_3</t>
+  </si>
+  <si>
+    <t>火焰_大_3</t>
+  </si>
+  <si>
+    <t>smoke_small_1</t>
+  </si>
+  <si>
+    <t>烟雾_小_1</t>
+  </si>
+  <si>
+    <t>smoke_middle_1</t>
+  </si>
+  <si>
+    <t>烟雾_中_1</t>
+  </si>
+  <si>
+    <t>smoke_big_1</t>
+  </si>
+  <si>
+    <t>烟雾_大_1</t>
+  </si>
+  <si>
+    <t>crashSmoke_small_1</t>
+  </si>
+  <si>
+    <t>坠地烟雾_小_1</t>
+  </si>
+  <si>
+    <t>crashSmoke_middle_1</t>
+  </si>
+  <si>
+    <t>坠地烟雾_中_1</t>
+  </si>
+  <si>
+    <t>crashSmoke_middle_2</t>
+  </si>
+  <si>
+    <t>坠地烟雾_中_2</t>
+  </si>
+  <si>
+    <t>crashSmoke_middle_3</t>
+  </si>
+  <si>
+    <t>坠地烟雾_中_3</t>
+  </si>
+  <si>
+    <t>crashSmoke_big_1</t>
+  </si>
+  <si>
+    <t>坠地烟雾_大_1</t>
+  </si>
+  <si>
+    <t>crashSmoke_big_2</t>
+  </si>
+  <si>
+    <t>坠地烟雾_大_2</t>
+  </si>
+  <si>
+    <t>crashSmoke_big_3</t>
+  </si>
+  <si>
+    <t>坠地烟雾_大_3</t>
+  </si>
+  <si>
+    <t>crashSmoke_big_4</t>
+  </si>
+  <si>
+    <t>坠地烟雾_大_4</t>
+  </si>
+  <si>
+    <t>dropSmoke_1</t>
+  </si>
+  <si>
+    <t>下坠烟雾1</t>
+  </si>
+  <si>
+    <t>dropSmoke_2</t>
+  </si>
+  <si>
+    <t>下坠烟雾2</t>
   </si>
 </sst>
 </file>
@@ -1846,7 +1984,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F88"/>
+  <dimension ref="A1:F111"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -3448,162 +3586,814 @@
         <v>188</v>
       </c>
     </row>
+    <row r="89" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A89" s="3"/>
+      <c r="B89" s="3">
+        <v>13101</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="90" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A90" s="3"/>
+      <c r="B90" s="3">
+        <v>13102</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="91" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A91" s="3"/>
+      <c r="B91" s="3">
+        <v>13103</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="92" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A92" s="3"/>
+      <c r="B92" s="3">
+        <v>13201</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="93" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A93" s="3"/>
+      <c r="B93" s="3">
+        <v>13202</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="94" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A94" s="3"/>
+      <c r="B94" s="3">
+        <v>13203</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="95" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A95" s="3"/>
+      <c r="B95" s="3">
+        <v>13204</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="96" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A96" s="3"/>
+      <c r="B96" s="3">
+        <v>13301</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="97" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A97" s="3"/>
+      <c r="B97" s="3">
+        <v>13302</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="98" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A98" s="3"/>
+      <c r="B98" s="3">
+        <v>13303</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="99" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A99" s="3"/>
+      <c r="B99" s="3">
+        <v>13401</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="100" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A100" s="3"/>
+      <c r="B100" s="3">
+        <v>13421</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="101" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A101" s="3"/>
+      <c r="B101" s="3">
+        <v>13441</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="102" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A102" s="3"/>
+      <c r="B102" s="3">
+        <v>13501</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="103" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A103" s="3"/>
+      <c r="B103" s="3">
+        <v>13521</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="104" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A104" s="3"/>
+      <c r="B104" s="3">
+        <v>13522</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="105" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A105" s="3"/>
+      <c r="B105" s="3">
+        <v>13523</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F105" s="3" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="106" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A106" s="3"/>
+      <c r="B106" s="3">
+        <v>13541</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="107" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A107" s="3"/>
+      <c r="B107" s="3">
+        <v>13542</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F107" s="3" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="108" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A108" s="3"/>
+      <c r="B108" s="3">
+        <v>13543</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="109" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A109" s="3"/>
+      <c r="B109" s="3">
+        <v>13544</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F109" s="3" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="110" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A110" s="3"/>
+      <c r="B110" s="3">
+        <v>13560</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="111" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A111" s="3"/>
+      <c r="B111" s="3">
+        <v>13561</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>234</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="E4">
-    <cfRule type="cellIs" dxfId="0" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="175" operator="equal">
       <formula>"子弹命中"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="174" operator="equal">
       <formula>"子弹发射"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="173" operator="equal">
       <formula>"子弹"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="172" operator="equal">
+      <formula>"爆炸"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="171" operator="equal">
+      <formula>"其他"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E34">
+    <cfRule type="cellIs" dxfId="4" priority="161" operator="equal">
+      <formula>"其他"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="162" operator="equal">
+      <formula>"爆炸"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="163" operator="equal">
+      <formula>"子弹"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="164" operator="equal">
+      <formula>"子弹发射"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="165" operator="equal">
+      <formula>"子弹命中"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E48">
+    <cfRule type="cellIs" dxfId="4" priority="156" operator="equal">
+      <formula>"其他"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="157" operator="equal">
+      <formula>"爆炸"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="158" operator="equal">
+      <formula>"子弹"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="159" operator="equal">
+      <formula>"子弹发射"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="160" operator="equal">
+      <formula>"子弹命中"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E79">
+    <cfRule type="cellIs" dxfId="4" priority="286" operator="equal">
+      <formula>"其他"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="287" operator="equal">
+      <formula>"爆炸"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="288" operator="equal">
+      <formula>"子弹"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="289" operator="equal">
+      <formula>"子弹发射"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="290" operator="equal">
+      <formula>"子弹命中"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E99">
+    <cfRule type="cellIs" dxfId="0" priority="70" operator="equal">
+      <formula>"子弹命中"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="59" operator="equal">
+      <formula>"子弹发射"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="48" operator="equal">
+      <formula>"子弹"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="37" operator="equal">
+      <formula>"爆炸"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="26" operator="equal">
+      <formula>"其他"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E100">
+    <cfRule type="cellIs" dxfId="0" priority="69" operator="equal">
+      <formula>"子弹命中"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="58" operator="equal">
+      <formula>"子弹发射"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="47" operator="equal">
+      <formula>"子弹"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="36" operator="equal">
+      <formula>"爆炸"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="25" operator="equal">
+      <formula>"其他"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E101">
+    <cfRule type="cellIs" dxfId="0" priority="68" operator="equal">
+      <formula>"子弹命中"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="57" operator="equal">
+      <formula>"子弹发射"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="46" operator="equal">
+      <formula>"子弹"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="35" operator="equal">
+      <formula>"爆炸"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="24" operator="equal">
+      <formula>"其他"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E102">
+    <cfRule type="cellIs" dxfId="0" priority="67" operator="equal">
+      <formula>"子弹命中"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="56" operator="equal">
+      <formula>"子弹发射"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="45" operator="equal">
+      <formula>"子弹"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="34" operator="equal">
+      <formula>"爆炸"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="23" operator="equal">
+      <formula>"其他"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E103">
+    <cfRule type="cellIs" dxfId="0" priority="66" operator="equal">
+      <formula>"子弹命中"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="55" operator="equal">
+      <formula>"子弹发射"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="44" operator="equal">
+      <formula>"子弹"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="33" operator="equal">
+      <formula>"爆炸"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="22" operator="equal">
+      <formula>"其他"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E104">
+    <cfRule type="cellIs" dxfId="0" priority="65" operator="equal">
+      <formula>"子弹命中"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="54" operator="equal">
+      <formula>"子弹发射"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="43" operator="equal">
+      <formula>"子弹"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="32" operator="equal">
+      <formula>"爆炸"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="21" operator="equal">
+      <formula>"其他"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E105">
+    <cfRule type="cellIs" dxfId="0" priority="64" operator="equal">
+      <formula>"子弹命中"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="53" operator="equal">
+      <formula>"子弹发射"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="42" operator="equal">
+      <formula>"子弹"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="31" operator="equal">
+      <formula>"爆炸"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="20" operator="equal">
+      <formula>"其他"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E106">
+    <cfRule type="cellIs" dxfId="0" priority="63" operator="equal">
+      <formula>"子弹命中"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="52" operator="equal">
+      <formula>"子弹发射"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="41" operator="equal">
+      <formula>"子弹"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="30" operator="equal">
+      <formula>"爆炸"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="19" operator="equal">
+      <formula>"其他"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E107">
+    <cfRule type="cellIs" dxfId="0" priority="62" operator="equal">
+      <formula>"子弹命中"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="51" operator="equal">
+      <formula>"子弹发射"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="40" operator="equal">
+      <formula>"子弹"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="29" operator="equal">
+      <formula>"爆炸"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="18" operator="equal">
+      <formula>"其他"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E108">
+    <cfRule type="cellIs" dxfId="0" priority="61" operator="equal">
+      <formula>"子弹命中"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="50" operator="equal">
+      <formula>"子弹发射"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="39" operator="equal">
+      <formula>"子弹"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="28" operator="equal">
+      <formula>"爆炸"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="17" operator="equal">
+      <formula>"其他"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E109">
+    <cfRule type="cellIs" dxfId="0" priority="60" operator="equal">
+      <formula>"子弹命中"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="49" operator="equal">
+      <formula>"子弹发射"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="38" operator="equal">
+      <formula>"子弹"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="27" operator="equal">
       <formula>"爆炸"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="4" priority="16" operator="equal">
       <formula>"其他"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E34">
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
+  <conditionalFormatting sqref="E5:E9">
+    <cfRule type="cellIs" dxfId="4" priority="206" operator="equal">
       <formula>"其他"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="207" operator="equal">
       <formula>"爆炸"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="208" operator="equal">
       <formula>"子弹"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="209" operator="equal">
       <formula>"子弹发射"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="210" operator="equal">
       <formula>"子弹命中"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E48">
+  <conditionalFormatting sqref="E10:E12">
+    <cfRule type="cellIs" dxfId="4" priority="185" operator="equal">
+      <formula>"其他"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="190" operator="equal">
+      <formula>"爆炸"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="195" operator="equal">
+      <formula>"子弹"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="200" operator="equal">
+      <formula>"子弹发射"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="205" operator="equal">
+      <formula>"子弹命中"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E13:E16">
+    <cfRule type="cellIs" dxfId="4" priority="176" operator="equal">
+      <formula>"其他"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="177" operator="equal">
+      <formula>"爆炸"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="178" operator="equal">
+      <formula>"子弹"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="179" operator="equal">
+      <formula>"子弹发射"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="180" operator="equal">
+      <formula>"子弹命中"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E80:E88">
+    <cfRule type="cellIs" dxfId="4" priority="246" operator="equal">
+      <formula>"其他"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="247" operator="equal">
+      <formula>"爆炸"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="248" operator="equal">
+      <formula>"子弹"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="249" operator="equal">
+      <formula>"子弹发射"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="250" operator="equal">
+      <formula>"子弹命中"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E89:E91">
+    <cfRule type="cellIs" dxfId="0" priority="155" operator="equal">
+      <formula>"子弹命中"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="142" operator="equal">
+      <formula>"子弹发射"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="129" operator="equal">
+      <formula>"子弹"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="116" operator="equal">
+      <formula>"爆炸"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="103" operator="equal">
+      <formula>"其他"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E92:E98">
+    <cfRule type="cellIs" dxfId="0" priority="90" operator="equal">
+      <formula>"子弹命中"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="89" operator="equal">
+      <formula>"子弹发射"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="88" operator="equal">
+      <formula>"子弹"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="87" operator="equal">
+      <formula>"爆炸"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="86" operator="equal">
+      <formula>"其他"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E110:E111">
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
+      <formula>"子弹命中"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
+      <formula>"子弹发射"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"子弹"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+      <formula>"爆炸"</formula>
+    </cfRule>
     <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>"其他"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E17:E33 E35:E47 E49:E78 E112:E1048576">
+    <cfRule type="cellIs" dxfId="4" priority="291" operator="equal">
+      <formula>"其他"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="292" operator="equal">
       <formula>"爆炸"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="293" operator="equal">
       <formula>"子弹"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="294" operator="equal">
       <formula>"子弹发射"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
-      <formula>"子弹命中"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E79">
-    <cfRule type="cellIs" dxfId="4" priority="131" operator="equal">
-      <formula>"其他"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="132" operator="equal">
-      <formula>"爆炸"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="133" operator="equal">
-      <formula>"子弹"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="134" operator="equal">
-      <formula>"子弹发射"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="135" operator="equal">
-      <formula>"子弹命中"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5:E9">
-    <cfRule type="cellIs" dxfId="4" priority="51" operator="equal">
-      <formula>"其他"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="52" operator="equal">
-      <formula>"爆炸"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="53" operator="equal">
-      <formula>"子弹"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="54" operator="equal">
-      <formula>"子弹发射"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="55" operator="equal">
-      <formula>"子弹命中"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E10:E12">
-    <cfRule type="cellIs" dxfId="4" priority="30" operator="equal">
-      <formula>"其他"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="35" operator="equal">
-      <formula>"爆炸"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="40" operator="equal">
-      <formula>"子弹"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="45" operator="equal">
-      <formula>"子弹发射"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="50" operator="equal">
-      <formula>"子弹命中"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E13:E16">
-    <cfRule type="cellIs" dxfId="4" priority="21" operator="equal">
-      <formula>"其他"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="22" operator="equal">
-      <formula>"爆炸"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="23" operator="equal">
-      <formula>"子弹"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="24" operator="equal">
-      <formula>"子弹发射"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="25" operator="equal">
-      <formula>"子弹命中"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E80:E88">
-    <cfRule type="cellIs" dxfId="4" priority="91" operator="equal">
-      <formula>"其他"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="92" operator="equal">
-      <formula>"爆炸"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="93" operator="equal">
-      <formula>"子弹"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="94" operator="equal">
-      <formula>"子弹发射"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="95" operator="equal">
-      <formula>"子弹命中"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E17:E33 E89:E1048576 E49:E78 E35:E47">
-    <cfRule type="cellIs" dxfId="4" priority="136" operator="equal">
-      <formula>"其他"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="137" operator="equal">
-      <formula>"爆炸"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="138" operator="equal">
-      <formula>"子弹"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="139" operator="equal">
-      <formula>"子弹发射"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="140" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="295" operator="equal">
       <formula>"子弹命中"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="E48 E4:E9 E10:E12 E13:E47 E49:E1048576">
+    <dataValidation type="list" sqref="E4:E109 E110:E111 E112:E1048576">
       <formula1>"其他,子弹发射,子弹,子弹命中,爆炸"</formula1>
     </dataValidation>
   </dataValidations>
